--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488180_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488180_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.0152</v>
+        <v>7.7045</v>
       </c>
       <c r="E2" t="n">
-        <v>6.901</v>
+        <v>6.2703</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1141</v>
+        <v>1.4342</v>
       </c>
       <c r="G2" t="n">
         <v>4.3264</v>
@@ -610,13 +610,13 @@
         <v>1.1117</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3003</v>
+        <v>0.9895</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3567</v>
+        <v>0.7259</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0565</v>
+        <v>0.2636</v>
       </c>
       <c r="V2" t="n">
         <v>2.2033</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.573</v>
+        <v>7.1074</v>
       </c>
       <c r="E3" t="n">
-        <v>5.979</v>
+        <v>6.9813</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5939</v>
+        <v>0.1261</v>
       </c>
       <c r="G3" t="n">
         <v>5.1872</v>
@@ -688,13 +688,13 @@
         <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7737000000000001</v>
+        <v>1.3082</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6392</v>
+        <v>0.3631</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4129</v>
+        <v>0.945</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3144</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.632</v>
+        <v>4.5713</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9431</v>
+        <v>4.6608</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3111</v>
+        <v>-0.0895</v>
       </c>
       <c r="G4" t="n">
         <v>0.7711</v>
@@ -766,13 +766,13 @@
         <v>1.6676</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2134</v>
+        <v>1.1528</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0496</v>
+        <v>0.7673</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1639</v>
+        <v>0.3855</v>
       </c>
       <c r="V4" t="n">
         <v>2.8327</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0667</v>
+        <v>3.7139</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3385</v>
+        <v>2.1334</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7282</v>
+        <v>1.5804</v>
       </c>
       <c r="G5" t="n">
         <v>4.4599</v>
@@ -844,13 +844,13 @@
         <v>1.6676</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3305</v>
+        <v>0.9777</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.475</v>
+        <v>0.3199</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8055</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0.3144</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.445</v>
+        <v>-0.0653</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7569</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2019</v>
+        <v>-1.0296</v>
       </c>
       <c r="G8" t="n">
         <v>0.6355</v>
@@ -1078,13 +1078,13 @@
         <v>0.7411</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3636</v>
+        <v>0.7433</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1467</v>
+        <v>0.0606</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5103</v>
+        <v>0.6827</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2589</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. USAOLA REDONDO</t>
+          <t>L. LOPEZ CALZADA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0853</v>
+        <v>-0.9379</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4294</v>
+        <v>-0.882</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5147</v>
+        <v>-0.0559</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6947</v>
+        <v>-1.3822</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1625</v>
+        <v>-3.6508</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8572</v>
+        <v>2.2686</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1615</v>
+        <v>-0.8115</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7514999999999999</v>
+        <v>-3.0415</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.59</v>
+        <v>2.23</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8561</v>
+        <v>-0.5707</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.589</v>
+        <v>-0.6093</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2671</v>
+        <v>0.0386</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.0382</v>
+        <v>-1.297</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.7793</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7411</v>
+        <v>1.4823</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1298</v>
+        <v>1.4263</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2151</v>
+        <v>0.5061</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0853</v>
+        <v>0.9202</v>
       </c>
       <c r="V9" t="n">
-        <v>2.5177</v>
+        <v>0.315</v>
       </c>
       <c r="W9" t="n">
-        <v>2.8321</v>
+        <v>2.2027</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3144</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. LOPEZ CALZADA</t>
+          <t>A. USAOLA REDONDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1266</v>
+        <v>-1.0677</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0461</v>
+        <v>0.3977</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0805</v>
+        <v>-1.4655</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3822</v>
+        <v>-1.6947</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.6508</v>
+        <v>0.1625</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2686</v>
+        <v>-1.8572</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8115</v>
+        <v>0.1615</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.0415</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>2.23</v>
+        <v>-0.59</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5707</v>
+        <v>-1.8561</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6093</v>
+        <v>-0.589</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0386</v>
+        <v>-1.2671</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.297</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.7793</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4823</v>
+        <v>0.7411</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2376</v>
+        <v>0.1474</v>
       </c>
       <c r="T10" t="n">
-        <v>0.342</v>
+        <v>0.1834</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8956</v>
+        <v>-0.0361</v>
       </c>
       <c r="V10" t="n">
-        <v>0.315</v>
+        <v>2.5177</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2027</v>
+        <v>2.8321</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8877</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4115</v>
+        <v>-1.1303</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2653</v>
+        <v>-0.058</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1462</v>
+        <v>-1.0723</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3725</v>
@@ -1312,13 +1312,13 @@
         <v>0.3706</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4096</v>
+        <v>-0.1284</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3283</v>
+        <v>-0.1209</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0813</v>
+        <v>-0.0075</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4616</v>
+        <v>-2.0448</v>
       </c>
       <c r="E12" t="n">
-        <v>1.0473</v>
+        <v>0.7103</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.509</v>
+        <v>-2.7552</v>
       </c>
       <c r="G12" t="n">
         <v>-0.0133</v>
@@ -1390,13 +1390,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5135999999999999</v>
+        <v>-0.0696</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3793</v>
+        <v>0.0423</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1343</v>
+        <v>-0.1119</v>
       </c>
       <c r="V12" t="n">
         <v>-2.5177</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.9451</v>
+        <v>20.0393</v>
       </c>
       <c r="E13" t="n">
-        <v>22.272</v>
+        <v>23.3662</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.327199999999999</v>
+        <v>-3.3273</v>
       </c>
       <c r="G13" t="n">
         <v>13.1056</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.5564</v>
+        <v>-5.556400000000001</v>
       </c>
       <c r="I13" t="n">
         <v>18.6621</v>
@@ -1453,7 +1453,7 @@
         <v>-8.407399999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.064800000000001</v>
+        <v>-7.0648</v>
       </c>
       <c r="O13" t="n">
         <v>-1.3426</v>
@@ -1468,13 +1468,13 @@
         <v>10.1908</v>
       </c>
       <c r="S13" t="n">
-        <v>5.452900000000001</v>
+        <v>6.5472</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7535</v>
+        <v>2.8477</v>
       </c>
       <c r="U13" t="n">
-        <v>3.6994</v>
+        <v>3.6993</v>
       </c>
       <c r="V13" t="n">
         <v>4.0921</v>
@@ -1483,13 +1483,13 @@
         <v>12.9018</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.809799999999999</v>
+        <v>-8.809800000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. HEPBURN</t>
+          <t>O. FAJANA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9305</v>
+        <v>2.0297</v>
       </c>
       <c r="E14" t="n">
-        <v>3.752</v>
+        <v>6.0924</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8215</v>
+        <v>-4.0627</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4467</v>
+        <v>-1.1677</v>
       </c>
       <c r="H14" t="n">
-        <v>5.7845</v>
+        <v>-0.0419</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.3378</v>
+        <v>-1.1259</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1884</v>
+        <v>2.6829</v>
       </c>
       <c r="K14" t="n">
-        <v>5.7583</v>
+        <v>0.6603</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5699</v>
+        <v>2.0227</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7417</v>
+        <v>-3.8507</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0262</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7678</v>
+        <v>-3.1485</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.2234</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8529</v>
+        <v>2.2234</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3159</v>
+        <v>-0.9137</v>
       </c>
       <c r="T14" t="n">
-        <v>0.102</v>
+        <v>-0.3665</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2139</v>
+        <v>-0.5472</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.8321</v>
+        <v>1.8877</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3144</v>
+        <v>3.776</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.1466</v>
+        <v>-1.8883</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. FAJANA</t>
+          <t>P. HEPBURN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4651</v>
+        <v>1.3252</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7986</v>
+        <v>3.2623</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.3335</v>
+        <v>-1.9372</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1677</v>
+        <v>4.4467</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0419</v>
+        <v>5.7845</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1259</v>
+        <v>-1.3378</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6829</v>
+        <v>5.1884</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6603</v>
+        <v>5.7583</v>
       </c>
       <c r="L15" t="n">
-        <v>2.0227</v>
+        <v>-0.5699</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.8507</v>
+        <v>-0.7417</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7020999999999999</v>
+        <v>0.0262</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.1485</v>
+        <v>-0.7678</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2234</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2234</v>
+        <v>1.8529</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4783</v>
+        <v>-0.2894</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6603</v>
+        <v>-0.3876</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8179999999999999</v>
+        <v>0.0982</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8877</v>
+        <v>-2.8321</v>
       </c>
       <c r="W15" t="n">
-        <v>3.776</v>
+        <v>0.3144</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8883</v>
+        <v>-3.1466</v>
       </c>
     </row>
     <row r="16">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1102</v>
+        <v>0.2162</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0461</v>
+        <v>1.242</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1563</v>
+        <v>-1.0258</v>
       </c>
       <c r="G17" t="n">
         <v>-2.9985</v>
@@ -1780,13 +1780,13 @@
         <v>2.7793</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4823</v>
+        <v>-1.1559</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0433</v>
+        <v>-0.8474</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.439</v>
+        <v>-0.3084</v>
       </c>
       <c r="V17" t="n">
         <v>2.5177</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6935</v>
+        <v>-2.4152</v>
       </c>
       <c r="E18" t="n">
         <v>-0.5635</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.13</v>
+        <v>-1.8517</v>
       </c>
       <c r="G18" t="n">
         <v>0.591</v>
@@ -1858,13 +1858,13 @@
         <v>0.7411</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2845</v>
+        <v>-0.0062</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1679</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1167</v>
+        <v>0.1616</v>
       </c>
       <c r="V18" t="n">
         <v>-1.8883</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7111</v>
+        <v>-2.6865</v>
       </c>
       <c r="E19" t="n">
         <v>-2.1698</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5413</v>
+        <v>-0.5167</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8208</v>
@@ -1936,13 +1936,13 @@
         <v>0.3706</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6489</v>
+        <v>-0.6243</v>
       </c>
       <c r="T19" t="n">
         <v>-0.2736</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3753</v>
+        <v>-0.3507</v>
       </c>
       <c r="V19" t="n">
         <v>0.3144</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>S. TRUJILLO SUAREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7857</v>
+        <v>-3.6439</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8171</v>
+        <v>0.583</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9686</v>
+        <v>-4.2269</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.9734</v>
+        <v>-2.2459</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4914</v>
+        <v>1.9579</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.482</v>
+        <v>-4.2038</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.6041</v>
+        <v>1.8655</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.77</v>
+        <v>2.3525</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1659</v>
+        <v>-0.487</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.3693</v>
+        <v>-4.1114</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2786</v>
+        <v>-0.3945</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.6478</v>
+        <v>-3.7168</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9264</v>
+        <v>2.4087</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5027</v>
+        <v>-1.0275</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0284</v>
+        <v>-0.7054</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4743</v>
+        <v>-0.3221</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.315</v>
+        <v>2.2022</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.2022</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1497</v>
+        <v>-4.3707</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6644</v>
+        <v>-0.7623</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4853</v>
+        <v>-3.6084</v>
       </c>
       <c r="G21" t="n">
         <v>-2.9016</v>
@@ -2092,13 +2092,13 @@
         <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5832000000000001</v>
+        <v>-0.8043</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.332</v>
+        <v>-0.4299</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2512</v>
+        <v>-0.3743</v>
       </c>
       <c r="V21" t="n">
         <v>-2.5177</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. TRUJILLO SUAREZ</t>
+          <t>M. KOZAR SIMIONIKA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5499</v>
+        <v>-4.7617</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2984</v>
+        <v>-2.4067</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.2515</v>
+        <v>-2.355</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2459</v>
+        <v>-2.9796</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9579</v>
+        <v>0.6239</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.2038</v>
+        <v>-3.6035</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8655</v>
+        <v>-1.0081</v>
       </c>
       <c r="K22" t="n">
-        <v>2.3525</v>
+        <v>0.2147</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.487</v>
+        <v>-1.2228</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.1114</v>
+        <v>-1.9715</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3945</v>
+        <v>0.4092</v>
       </c>
       <c r="O22" t="n">
-        <v>-3.7168</v>
+        <v>-2.3807</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3706</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4087</v>
+        <v>0.7411</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9335</v>
+        <v>-0.3379</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.5867</v>
+        <v>-0.4722</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3467</v>
+        <v>0.1343</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W22" t="n">
-        <v>2.2022</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.2022</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. KOZAR SIMIONIKA</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2845</v>
+        <v>-4.9293</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7005</v>
+        <v>-2.8944</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.584</v>
+        <v>-2.035</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9796</v>
+        <v>-4.9734</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6239</v>
+        <v>-1.4914</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.6035</v>
+        <v>-3.482</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0081</v>
+        <v>-1.6041</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2147</v>
+        <v>-1.77</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2228</v>
+        <v>0.1659</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9715</v>
+        <v>-3.3693</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4092</v>
+        <v>0.2786</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.3807</v>
+        <v>-3.6478</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8608</v>
+        <v>0.3591</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.766</v>
+        <v>-0.0488</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0948</v>
+        <v>0.4079</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2589</v>
+        <v>-0.315</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-18.9449</v>
+        <v>-18.2921</v>
       </c>
       <c r="E24" t="n">
-        <v>3.327099999999999</v>
+        <v>3.3271</v>
       </c>
       <c r="F24" t="n">
-        <v>-22.272</v>
+        <v>-21.6194</v>
       </c>
       <c r="G24" t="n">
         <v>-13.1057</v>
       </c>
       <c r="H24" t="n">
-        <v>5.556400000000001</v>
+        <v>5.5564</v>
       </c>
       <c r="I24" t="n">
         <v>-18.6621</v>
@@ -2302,7 +2302,7 @@
         <v>8.407399999999997</v>
       </c>
       <c r="K24" t="n">
-        <v>7.0649</v>
+        <v>7.064900000000002</v>
       </c>
       <c r="L24" t="n">
         <v>1.3428</v>
@@ -2326,19 +2326,19 @@
         <v>13.8964</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.452900000000001</v>
+        <v>-4.8001</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.6994</v>
+        <v>-3.6993</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.7535</v>
+        <v>-1.1007</v>
       </c>
       <c r="V24" t="n">
         <v>-4.0922</v>
       </c>
       <c r="W24" t="n">
-        <v>8.809699999999999</v>
+        <v>8.809700000000001</v>
       </c>
       <c r="X24" t="n">
         <v>-12.902</v>
